--- a/docs/sprint2/task-board.xlsx
+++ b/docs/sprint2/task-board.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="66">
   <si>
     <t>ТАБЛИЦЯ РОЗПОДІЛУ ЗАДАЧ СПРИНТА (Шаблон 2)</t>
   </si>
@@ -151,6 +151,9 @@
     <t>docs/sprint2/requirements-defects.xlsx (аркуш Спірні)</t>
   </si>
   <si>
+    <t>Дубчак Богдан</t>
+  </si>
+  <si>
     <t>Підготовка виправленої специфікації вимог SRS 1.1 та оформлення журналу змін</t>
   </si>
   <si>
@@ -164,9 +167,6 @@
   </si>
   <si>
     <t>Оніщук Ілля</t>
-  </si>
-  <si>
-    <t>на рев'ю</t>
   </si>
   <si>
     <t>docs/sprint2/test-plan.md (розд. 1, 5, 6)</t>
@@ -188,12 +188,6 @@
   </si>
   <si>
     <t>СМ</t>
-  </si>
-  <si>
-    <t>Дубчак Богдан</t>
-  </si>
-  <si>
-    <t>в процесі</t>
   </si>
   <si>
     <t>docs/sprint2/task-board.xlsx, docs/team/charter.md</t>
@@ -234,17 +228,14 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12.0"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="14.0"/>
       <color rgb="FF1E2D60"/>
       <name val="Arial"/>
-      <scheme val="minor"/>
     </font>
     <font/>
     <font>
@@ -252,62 +243,52 @@
       <sz val="12.0"/>
       <color rgb="FF596072"/>
       <name val="Arial"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12.0"/>
+      <color rgb="FF191926"/>
+      <name val="Arial"/>
     </font>
     <font>
       <b/>
       <sz val="12.0"/>
       <color rgb="FF424759"/>
       <name val="Arial"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12.0"/>
-      <color rgb="FF191926"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="12.0"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="12.0"/>
       <color rgb="FF1E2D60"/>
       <name val="Arial"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12.0"/>
+      <color theme="1"/>
+      <name val="Arial"/>
     </font>
     <font>
       <u/>
       <sz val="12.0"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
       <sz val="12.0"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
       <sz val="12.0"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="12.0"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="9">
@@ -769,185 +750,129 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="60">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
     <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf borderId="2" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="4" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="5" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="6" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="7" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" vertical="center"/>
+    <xf borderId="7" fillId="4" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="8" fillId="5" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="8" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="8" fillId="5" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="8" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="9" fillId="5" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" vertical="center"/>
-    </xf>
+    <xf borderId="9" fillId="5" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
     <xf borderId="10" fillId="6" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf borderId="11" fillId="6" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf borderId="12" fillId="6" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="13" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" vertical="center"/>
+    <xf borderId="13" fillId="4" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="14" fillId="5" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="14" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="14" fillId="5" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="14" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="15" fillId="5" fontId="6" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" readingOrder="0" vertical="center"/>
-    </xf>
+    <xf borderId="15" fillId="5" fontId="5" numFmtId="164" xfId="0" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="16" fillId="7" fontId="8" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf borderId="17" fillId="7" fontId="8" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf borderId="18" fillId="7" fontId="8" numFmtId="166" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf borderId="19" fillId="6" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="20" fillId="6" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="21" fillId="6" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="22" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="23" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="23" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="23" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="23" fillId="0" fontId="1" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0" vertical="center"/>
+    <xf borderId="22" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf borderId="23" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+      <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="24" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" vertical="center"/>
+    <xf borderId="23" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center"/>
     </xf>
+    <xf borderId="23" fillId="0" fontId="9" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="23" fillId="0" fontId="9" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf borderId="23" fillId="0" fontId="1" numFmtId="165" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="23" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="24" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
+      <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="25" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf borderId="25" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="25" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    <xf borderId="25" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="25" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" vertical="center"/>
+    <xf borderId="25" fillId="0" fontId="9" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="25" fillId="0" fontId="9" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="25" fillId="0" fontId="1" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0" vertical="center"/>
+    <xf borderId="25" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="25" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf borderId="26" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="25" fillId="8" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="26" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" vertical="center"/>
+    <xf borderId="25" fillId="8" fontId="9" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="25" fillId="8" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf borderId="25" fillId="8" fontId="1" numFmtId="165" xfId="0" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="25" fillId="8" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="25" fillId="8" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    <xf borderId="0" fillId="0" fontId="9" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="25" fillId="8" fontId="1" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="25" fillId="8" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="26" fillId="8" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="25" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="25" fillId="8" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="27" fillId="8" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="27" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="25" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="25" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="25" fillId="0" fontId="1" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf borderId="25" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf borderId="27" fillId="8" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="25" fillId="8" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="25" fillId="8" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="25" fillId="8" fontId="1" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf borderId="25" fillId="8" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+    <xf borderId="25" fillId="0" fontId="1" numFmtId="165" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="26" fillId="0" fontId="9" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="27" fillId="8" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="25" fillId="8" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="25" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="27" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="25" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="27" fillId="8" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="25" fillId="8" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
     <xf borderId="28" fillId="4" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" vertical="center"/>
+      <alignment horizontal="right"/>
     </xf>
     <xf borderId="29" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="30" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="31" fillId="4" fontId="8" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" vertical="center"/>
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="31" fillId="4" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="32" fillId="4" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf borderId="31" fillId="4" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="32" fillId="4" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -1212,6 +1137,22 @@
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
       <c r="I2" s="4"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
+      <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
+      <c r="T2" s="1"/>
+      <c r="U2" s="1"/>
+      <c r="V2" s="1"/>
+      <c r="W2" s="1"/>
+      <c r="X2" s="1"/>
+      <c r="Y2" s="1"/>
     </row>
     <row r="3">
       <c r="A3" s="5" t="s">
@@ -1336,7 +1277,7 @@
       </c>
       <c r="I6" s="21">
         <f>IF(COUNTA(B11:B27)=0, 0, COUNTIF(G11:G27, "готово") / COUNTA(B11:B27))</f>
-        <v>0.5384615385</v>
+        <v>0.9230769231</v>
       </c>
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
@@ -1443,15 +1384,15 @@
       <c r="E9" s="29">
         <v>2.5</v>
       </c>
-      <c r="F9" s="29"/>
+      <c r="F9" s="30"/>
       <c r="G9" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="H9" s="30" t="s">
+      <c r="H9" s="31" t="s">
         <v>23</v>
       </c>
-      <c r="I9" s="31"/>
-      <c r="J9" s="32"/>
+      <c r="I9" s="32"/>
+      <c r="J9" s="33"/>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
@@ -1484,15 +1425,15 @@
       <c r="E10" s="29">
         <v>2.5</v>
       </c>
-      <c r="F10" s="29"/>
+      <c r="F10" s="30"/>
       <c r="G10" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="H10" s="30" t="s">
+      <c r="H10" s="31" t="s">
         <v>23</v>
       </c>
-      <c r="I10" s="31"/>
-      <c r="J10" s="32"/>
+      <c r="I10" s="32"/>
+      <c r="J10" s="33"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
@@ -1513,29 +1454,29 @@
       <c r="A11" s="25">
         <v>3.0</v>
       </c>
-      <c r="B11" s="33" t="s">
+      <c r="B11" s="34" t="s">
         <v>27</v>
       </c>
-      <c r="C11" s="34" t="s">
+      <c r="C11" s="35" t="s">
         <v>28</v>
       </c>
-      <c r="D11" s="35" t="s">
+      <c r="D11" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="E11" s="36">
+      <c r="E11" s="37">
         <v>2.5</v>
       </c>
-      <c r="F11" s="36">
+      <c r="F11" s="37">
         <v>2.0</v>
       </c>
-      <c r="G11" s="34" t="s">
+      <c r="G11" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="H11" s="37" t="s">
+      <c r="H11" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="I11" s="38"/>
-      <c r="J11" s="32"/>
+      <c r="I11" s="39"/>
+      <c r="J11" s="33"/>
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
@@ -1556,26 +1497,26 @@
       <c r="A12" s="25">
         <v>4.0</v>
       </c>
-      <c r="B12" s="39" t="s">
+      <c r="B12" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="40" t="s">
+      <c r="C12" s="35" t="s">
         <v>25</v>
       </c>
-      <c r="D12" s="35" t="s">
+      <c r="D12" s="36" t="s">
         <v>31</v>
       </c>
       <c r="E12" s="41">
         <v>2.5</v>
       </c>
-      <c r="F12" s="41"/>
-      <c r="G12" s="40" t="s">
+      <c r="F12" s="42"/>
+      <c r="G12" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="H12" s="42" t="s">
+      <c r="H12" s="43" t="s">
         <v>23</v>
       </c>
-      <c r="I12" s="43"/>
+      <c r="I12" s="39"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
@@ -1597,26 +1538,26 @@
       <c r="A13" s="25">
         <v>5.0</v>
       </c>
-      <c r="B13" s="33" t="s">
+      <c r="B13" s="34" t="s">
         <v>32</v>
       </c>
-      <c r="C13" s="34" t="s">
+      <c r="C13" s="35" t="s">
         <v>33</v>
       </c>
-      <c r="D13" s="35" t="s">
+      <c r="D13" s="36" t="s">
         <v>34</v>
       </c>
       <c r="E13" s="44">
         <v>2.5</v>
       </c>
-      <c r="F13" s="36"/>
-      <c r="G13" s="34" t="s">
+      <c r="F13" s="45"/>
+      <c r="G13" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="H13" s="45" t="s">
+      <c r="H13" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="I13" s="38"/>
+      <c r="I13" s="39"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
@@ -1638,13 +1579,13 @@
       <c r="A14" s="25">
         <v>6.0</v>
       </c>
-      <c r="B14" s="39" t="s">
+      <c r="B14" s="40" t="s">
         <v>35</v>
       </c>
-      <c r="C14" s="40" t="s">
+      <c r="C14" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="D14" s="35" t="s">
+      <c r="D14" s="36" t="s">
         <v>37</v>
       </c>
       <c r="E14" s="41">
@@ -1653,13 +1594,13 @@
       <c r="F14" s="41">
         <v>2.0</v>
       </c>
-      <c r="G14" s="40" t="s">
+      <c r="G14" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="H14" s="42" t="s">
+      <c r="H14" s="43" t="s">
         <v>23</v>
       </c>
-      <c r="I14" s="43"/>
+      <c r="I14" s="39"/>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
@@ -1681,26 +1622,26 @@
       <c r="A15" s="25">
         <v>7.0</v>
       </c>
-      <c r="B15" s="33" t="s">
+      <c r="B15" s="34" t="s">
         <v>38</v>
       </c>
-      <c r="C15" s="34" t="s">
+      <c r="C15" s="35" t="s">
         <v>39</v>
       </c>
-      <c r="D15" s="35" t="s">
+      <c r="D15" s="36" t="s">
         <v>40</v>
       </c>
-      <c r="E15" s="36">
+      <c r="E15" s="37">
         <v>3.5</v>
       </c>
-      <c r="F15" s="36"/>
-      <c r="G15" s="34" t="s">
+      <c r="F15" s="45"/>
+      <c r="G15" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="H15" s="33" t="s">
+      <c r="H15" s="34" t="s">
         <v>41</v>
       </c>
-      <c r="I15" s="38" t="s">
+      <c r="I15" s="46" t="s">
         <v>42</v>
       </c>
       <c r="J15" s="1"/>
@@ -1724,26 +1665,28 @@
       <c r="A16" s="25">
         <v>8.0</v>
       </c>
-      <c r="B16" s="39" t="s">
+      <c r="B16" s="40" t="s">
         <v>43</v>
       </c>
-      <c r="C16" s="40" t="s">
+      <c r="C16" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="D16" s="46" t="s">
+      <c r="D16" s="36" t="s">
         <v>42</v>
       </c>
       <c r="E16" s="41">
         <v>2.0</v>
       </c>
-      <c r="F16" s="41"/>
-      <c r="G16" s="40" t="s">
+      <c r="F16" s="42"/>
+      <c r="G16" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="H16" s="39" t="s">
+      <c r="H16" s="40" t="s">
         <v>45</v>
       </c>
-      <c r="I16" s="43"/>
+      <c r="I16" s="46" t="s">
+        <v>46</v>
+      </c>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
       <c r="L16" s="1"/>
@@ -1765,26 +1708,28 @@
       <c r="A17" s="25">
         <v>9.0</v>
       </c>
-      <c r="B17" s="33" t="s">
+      <c r="B17" s="34" t="s">
+        <v>47</v>
+      </c>
+      <c r="C17" s="35" t="s">
+        <v>39</v>
+      </c>
+      <c r="D17" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="E17" s="37">
+        <v>3.5</v>
+      </c>
+      <c r="F17" s="45"/>
+      <c r="G17" s="35" t="s">
+        <v>22</v>
+      </c>
+      <c r="H17" s="34" t="s">
+        <v>48</v>
+      </c>
+      <c r="I17" s="46" t="s">
         <v>46</v>
       </c>
-      <c r="C17" s="34" t="s">
-        <v>39</v>
-      </c>
-      <c r="D17" s="35" t="s">
-        <v>40</v>
-      </c>
-      <c r="E17" s="36">
-        <v>3.5</v>
-      </c>
-      <c r="F17" s="36"/>
-      <c r="G17" s="34" t="s">
-        <v>22</v>
-      </c>
-      <c r="H17" s="33" t="s">
-        <v>47</v>
-      </c>
-      <c r="I17" s="38"/>
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
       <c r="L17" s="1"/>
@@ -1806,26 +1751,26 @@
       <c r="A18" s="25">
         <v>10.0</v>
       </c>
-      <c r="B18" s="39" t="s">
-        <v>48</v>
-      </c>
-      <c r="C18" s="40" t="s">
+      <c r="B18" s="40" t="s">
         <v>49</v>
       </c>
-      <c r="D18" s="46" t="s">
+      <c r="C18" s="35" t="s">
         <v>50</v>
+      </c>
+      <c r="D18" s="36" t="s">
+        <v>51</v>
       </c>
       <c r="E18" s="41">
         <v>3.0</v>
       </c>
-      <c r="F18" s="41"/>
-      <c r="G18" s="40" t="s">
-        <v>51</v>
+      <c r="F18" s="42"/>
+      <c r="G18" s="35" t="s">
+        <v>22</v>
       </c>
-      <c r="H18" s="39" t="s">
+      <c r="H18" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="I18" s="43" t="s">
+      <c r="I18" s="46" t="s">
         <v>40</v>
       </c>
       <c r="J18" s="1"/>
@@ -1849,26 +1794,26 @@
       <c r="A19" s="25">
         <v>11.0</v>
       </c>
-      <c r="B19" s="33" t="s">
+      <c r="B19" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="C19" s="34" t="s">
-        <v>49</v>
-      </c>
-      <c r="D19" s="35" t="s">
+      <c r="C19" s="35" t="s">
         <v>50</v>
       </c>
-      <c r="E19" s="36">
+      <c r="D19" s="36" t="s">
+        <v>51</v>
+      </c>
+      <c r="E19" s="37">
         <v>3.5</v>
       </c>
-      <c r="F19" s="36"/>
-      <c r="G19" s="34" t="s">
-        <v>51</v>
+      <c r="F19" s="45"/>
+      <c r="G19" s="35" t="s">
+        <v>22</v>
       </c>
-      <c r="H19" s="33" t="s">
+      <c r="H19" s="34" t="s">
         <v>54</v>
       </c>
-      <c r="I19" s="38" t="s">
+      <c r="I19" s="46" t="s">
         <v>40</v>
       </c>
       <c r="J19" s="1"/>
@@ -1892,26 +1837,26 @@
       <c r="A20" s="25">
         <v>12.0</v>
       </c>
-      <c r="B20" s="39" t="s">
+      <c r="B20" s="40" t="s">
         <v>55</v>
       </c>
-      <c r="C20" s="40" t="s">
-        <v>49</v>
+      <c r="C20" s="35" t="s">
+        <v>50</v>
       </c>
-      <c r="D20" s="46" t="s">
-        <v>50</v>
+      <c r="D20" s="36" t="s">
+        <v>51</v>
       </c>
       <c r="E20" s="41">
         <v>1.5</v>
       </c>
-      <c r="F20" s="41"/>
-      <c r="G20" s="40" t="s">
-        <v>51</v>
+      <c r="F20" s="42"/>
+      <c r="G20" s="35" t="s">
+        <v>22</v>
       </c>
-      <c r="H20" s="39" t="s">
+      <c r="H20" s="40" t="s">
         <v>56</v>
       </c>
-      <c r="I20" s="43" t="s">
+      <c r="I20" s="46" t="s">
         <v>40</v>
       </c>
       <c r="J20" s="1"/>
@@ -1935,26 +1880,28 @@
       <c r="A21" s="25">
         <v>13.0</v>
       </c>
-      <c r="B21" s="33" t="s">
+      <c r="B21" s="34" t="s">
         <v>57</v>
       </c>
-      <c r="C21" s="34" t="s">
+      <c r="C21" s="35" t="s">
         <v>58</v>
       </c>
-      <c r="D21" s="35" t="s">
+      <c r="D21" s="36" t="s">
+        <v>46</v>
+      </c>
+      <c r="E21" s="37">
+        <v>2.5</v>
+      </c>
+      <c r="F21" s="45"/>
+      <c r="G21" s="35" t="s">
+        <v>22</v>
+      </c>
+      <c r="H21" s="34" t="s">
         <v>59</v>
       </c>
-      <c r="E21" s="36">
-        <v>2.5</v>
+      <c r="I21" s="46" t="s">
+        <v>42</v>
       </c>
-      <c r="F21" s="36"/>
-      <c r="G21" s="34" t="s">
-        <v>60</v>
-      </c>
-      <c r="H21" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="I21" s="38"/>
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
       <c r="L21" s="1"/>
@@ -1976,26 +1923,28 @@
       <c r="A22" s="25">
         <v>14.0</v>
       </c>
-      <c r="B22" s="39" t="s">
-        <v>62</v>
+      <c r="B22" s="40" t="s">
+        <v>60</v>
       </c>
-      <c r="C22" s="40" t="s">
+      <c r="C22" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="D22" s="46" t="s">
+      <c r="D22" s="36" t="s">
         <v>42</v>
       </c>
       <c r="E22" s="41">
         <v>2.0</v>
       </c>
-      <c r="F22" s="41"/>
-      <c r="G22" s="40" t="s">
-        <v>60</v>
+      <c r="F22" s="42"/>
+      <c r="G22" s="35" t="s">
+        <v>22</v>
       </c>
-      <c r="H22" s="39" t="s">
-        <v>63</v>
+      <c r="H22" s="40" t="s">
+        <v>61</v>
       </c>
-      <c r="I22" s="43"/>
+      <c r="I22" s="46" t="s">
+        <v>46</v>
+      </c>
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
       <c r="L22" s="1"/>
@@ -2017,26 +1966,26 @@
       <c r="A23" s="25">
         <v>15.0</v>
       </c>
-      <c r="B23" s="33" t="s">
+      <c r="B23" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="C23" s="35" t="s">
+        <v>58</v>
+      </c>
+      <c r="D23" s="36" t="s">
+        <v>46</v>
+      </c>
+      <c r="E23" s="37">
+        <v>1.0</v>
+      </c>
+      <c r="F23" s="45"/>
+      <c r="G23" s="35" t="s">
+        <v>63</v>
+      </c>
+      <c r="H23" s="34" t="s">
         <v>64</v>
       </c>
-      <c r="C23" s="34" t="s">
-        <v>58</v>
-      </c>
-      <c r="D23" s="35" t="s">
-        <v>59</v>
-      </c>
-      <c r="E23" s="36">
-        <v>1.0</v>
-      </c>
-      <c r="F23" s="36"/>
-      <c r="G23" s="34" t="s">
-        <v>65</v>
-      </c>
-      <c r="H23" s="33" t="s">
-        <v>66</v>
-      </c>
-      <c r="I23" s="38"/>
+      <c r="I23" s="39"/>
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
@@ -2056,14 +2005,14 @@
     </row>
     <row r="24">
       <c r="A24" s="47"/>
-      <c r="B24" s="39"/>
-      <c r="C24" s="40"/>
-      <c r="D24" s="46"/>
-      <c r="E24" s="41"/>
-      <c r="F24" s="41"/>
-      <c r="G24" s="40"/>
-      <c r="H24" s="39"/>
-      <c r="I24" s="43"/>
+      <c r="B24" s="48"/>
+      <c r="C24" s="49"/>
+      <c r="D24" s="49"/>
+      <c r="E24" s="42"/>
+      <c r="F24" s="42"/>
+      <c r="G24" s="49"/>
+      <c r="H24" s="48"/>
+      <c r="I24" s="39"/>
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
       <c r="L24" s="1"/>
@@ -2082,15 +2031,15 @@
       <c r="Y24" s="1"/>
     </row>
     <row r="25">
-      <c r="A25" s="48"/>
-      <c r="B25" s="49"/>
-      <c r="C25" s="50"/>
-      <c r="D25" s="46"/>
-      <c r="E25" s="51"/>
-      <c r="F25" s="51"/>
-      <c r="G25" s="50"/>
-      <c r="H25" s="52"/>
-      <c r="I25" s="43"/>
+      <c r="A25" s="50"/>
+      <c r="B25" s="51"/>
+      <c r="C25" s="51"/>
+      <c r="D25" s="49"/>
+      <c r="E25" s="45"/>
+      <c r="F25" s="45"/>
+      <c r="G25" s="51"/>
+      <c r="H25" s="51"/>
+      <c r="I25" s="39"/>
       <c r="J25" s="1"/>
       <c r="K25" s="1"/>
       <c r="L25" s="1"/>
@@ -2109,15 +2058,15 @@
       <c r="Y25" s="1"/>
     </row>
     <row r="26">
-      <c r="A26" s="53"/>
-      <c r="B26" s="54"/>
-      <c r="C26" s="55"/>
-      <c r="D26" s="46"/>
-      <c r="E26" s="56"/>
-      <c r="F26" s="56"/>
-      <c r="G26" s="55"/>
-      <c r="H26" s="57"/>
-      <c r="I26" s="43"/>
+      <c r="A26" s="52"/>
+      <c r="B26" s="53"/>
+      <c r="C26" s="51"/>
+      <c r="D26" s="49"/>
+      <c r="E26" s="42"/>
+      <c r="F26" s="42"/>
+      <c r="G26" s="51"/>
+      <c r="H26" s="53"/>
+      <c r="I26" s="39"/>
       <c r="J26" s="1"/>
       <c r="K26" s="1"/>
       <c r="L26" s="1"/>
@@ -2136,15 +2085,15 @@
       <c r="Y26" s="1"/>
     </row>
     <row r="27">
-      <c r="A27" s="48"/>
-      <c r="B27" s="49"/>
-      <c r="C27" s="50"/>
-      <c r="D27" s="46"/>
-      <c r="E27" s="51"/>
-      <c r="F27" s="51"/>
-      <c r="G27" s="50"/>
-      <c r="H27" s="52"/>
-      <c r="I27" s="43"/>
+      <c r="A27" s="50"/>
+      <c r="B27" s="51"/>
+      <c r="C27" s="51"/>
+      <c r="D27" s="49"/>
+      <c r="E27" s="45"/>
+      <c r="F27" s="45"/>
+      <c r="G27" s="51"/>
+      <c r="H27" s="51"/>
+      <c r="I27" s="39"/>
       <c r="J27" s="1"/>
       <c r="K27" s="1"/>
       <c r="L27" s="1"/>
@@ -2163,23 +2112,23 @@
       <c r="Y27" s="1"/>
     </row>
     <row r="28">
-      <c r="A28" s="58" t="s">
-        <v>67</v>
+      <c r="A28" s="54" t="s">
+        <v>65</v>
       </c>
-      <c r="B28" s="59"/>
-      <c r="C28" s="59"/>
-      <c r="D28" s="60"/>
-      <c r="E28" s="61">
+      <c r="B28" s="55"/>
+      <c r="C28" s="55"/>
+      <c r="D28" s="56"/>
+      <c r="E28" s="57">
         <f t="shared" ref="E28:F28" si="2">SUM(E11:E27)</f>
         <v>32</v>
       </c>
-      <c r="F28" s="61">
+      <c r="F28" s="57">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="G28" s="62"/>
-      <c r="H28" s="62"/>
-      <c r="I28" s="63"/>
+      <c r="G28" s="58"/>
+      <c r="H28" s="58"/>
+      <c r="I28" s="59"/>
       <c r="J28" s="1"/>
       <c r="K28" s="1"/>
       <c r="L28" s="1"/>
